--- a/data/raw/inventory/Week 26/Tonor/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 26/Tonor/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 26\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FA6113-634A-4C7B-804E-C059A500AB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA61C0FD-D88F-444D-9639-B9838543833C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -204,13 +204,13 @@
     <t>B07TSN2H9D</t>
   </si>
   <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
     <t>AMPM</t>
   </si>
   <si>
     <t>B2B - AMPM</t>
+  </si>
+  <si>
+    <t>Open Order</t>
   </si>
 </sst>
 </file>
@@ -872,7 +872,7 @@
         <v>322</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -889,7 +889,7 @@
         <v>8</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -940,7 +940,7 @@
         <v>103</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -957,7 +957,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -974,7 +974,7 @@
         <v>49</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -991,7 +991,7 @@
         <v>130</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1008,7 +1008,7 @@
         <v>551</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1025,7 +1025,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1042,7 +1042,7 @@
         <v>98</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1059,7 +1059,7 @@
         <v>140</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1076,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1093,7 +1093,7 @@
         <v>12</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1110,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1127,7 +1127,7 @@
         <v>28</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1144,7 +1144,7 @@
         <v>19</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1161,7 +1161,7 @@
         <v>323</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1178,7 +1178,7 @@
         <v>263</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1195,7 +1195,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1229,37 +1229,37 @@
         <v>80</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K23" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L23" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A20">
+    <cfRule type="duplicateValues" dxfId="10" priority="2199"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="10" priority="2162"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2163"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2162"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="duplicateValues" dxfId="7" priority="2196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1919"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2130"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2131" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2131" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="1917"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1918" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1917"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1918" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1915"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1916" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="2196"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="2199"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1916" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
